--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PASTILHA DE FREIO 08_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PASTILHA DE FREIO 08_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,11 @@
           <t>21</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,7 +507,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +532,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +557,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +582,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,7 +607,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -608,7 +632,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,7 +657,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -650,7 +682,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -671,7 +707,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,7 +757,11 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -738,7 +782,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -759,7 +807,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -780,7 +832,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -801,7 +857,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -847,7 +907,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -868,7 +932,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -889,7 +957,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -935,7 +1007,11 @@
           <t>19</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -956,7 +1032,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -977,7 +1057,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -998,7 +1082,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1019,7 +1107,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1040,7 +1132,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1061,7 +1157,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1107,7 +1207,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1128,7 +1232,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1149,7 +1257,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1170,7 +1282,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1191,7 +1307,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1212,7 +1332,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1233,7 +1357,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1254,7 +1382,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1275,7 +1407,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1296,7 +1432,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1317,7 +1457,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1338,7 +1482,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1359,7 +1507,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1380,7 +1532,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1401,7 +1557,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1422,7 +1582,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1443,7 +1607,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1464,7 +1632,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1506,7 +1678,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1527,7 +1703,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1548,7 +1728,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1569,7 +1753,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1586,7 +1774,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1607,7 +1799,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1628,7 +1824,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1649,7 +1849,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1670,7 +1874,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1716,7 +1924,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1737,7 +1949,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1783,7 +1999,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1804,7 +2024,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1825,7 +2049,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1846,7 +2074,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1867,7 +2099,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1888,7 +2124,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1909,7 +2149,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1930,7 +2174,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1951,7 +2199,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1972,33 +2224,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 751320982285</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PASTILHA DE FREIO 08_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PASTILHA DE FREIO 08_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -782,11 +712,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -807,11 +732,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -832,11 +752,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -857,11 +772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -882,11 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -907,11 +812,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -932,11 +832,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -957,11 +852,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -982,11 +872,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1007,11 +892,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1032,11 +912,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1057,11 +932,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1082,11 +952,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1107,11 +972,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1132,11 +992,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1157,11 +1012,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1182,11 +1032,6 @@
           <t>17</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1207,11 +1052,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1232,11 +1072,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1257,11 +1092,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1282,11 +1112,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1307,11 +1132,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1332,11 +1152,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1357,11 +1172,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1382,11 +1192,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1407,11 +1212,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1432,11 +1232,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1457,11 +1252,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1482,11 +1272,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1507,11 +1292,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1532,11 +1312,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1557,11 +1332,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1582,11 +1352,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1607,11 +1372,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1632,11 +1392,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1657,11 +1412,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1678,11 +1428,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1703,11 +1448,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1728,11 +1468,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1753,11 +1488,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1774,11 +1504,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1799,11 +1524,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1824,11 +1544,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1849,11 +1564,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1874,11 +1584,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1899,11 +1604,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1924,11 +1624,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1949,11 +1644,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1974,11 +1664,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1999,11 +1684,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2024,11 +1704,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2049,11 +1724,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2074,11 +1744,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2099,11 +1764,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2124,11 +1784,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2149,11 +1804,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2174,11 +1824,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2199,11 +1844,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2222,11 +1862,6 @@
       <c r="D73" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
     </row>
